--- a/data/processed/harmonization/Isotopes__Soil_nitrogen_delta15N/10.3334_cdiac_ornlsfa.010/10.3334_cdiac_ornlsfa.010_soil_Isotopes__Soil_nitrogen_delta15N.xlsx
+++ b/data/processed/harmonization/Isotopes__Soil_nitrogen_delta15N/10.3334_cdiac_ornlsfa.010/10.3334_cdiac_ornlsfa.010_soil_Isotopes__Soil_nitrogen_delta15N.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1:27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -562,12 +562,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>2:28</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -606,12 +606,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>3:31</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -650,12 +650,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>3:211</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -694,12 +694,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>1:219</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -738,12 +738,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>2:223</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -782,12 +782,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>3:243</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -826,12 +826,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>2:245</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -870,12 +870,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>1:247</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -914,12 +914,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>2:420</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -958,12 +958,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>1:421</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>3:117</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>1:123</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>2:125</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>2:302</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>3:308</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>1:319</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>1:355</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1310,12 +1310,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>3:364</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>2:376</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>3:517</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1442,12 +1442,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>1:523</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>2:577</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>1:588</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>3:591</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>1:704</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>3:711</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Sample_ID</t>
+          <t>Rep:Sample_ID</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
